--- a/storage/app/templates/documents/TEMPLAT_KONTRAK_DPUPR.xlsx
+++ b/storage/app/templates/documents/TEMPLAT_KONTRAK_DPUPR.xlsx
@@ -1,29 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALFIAN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPS\laragon\www\sipraja\storage\app\templates\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10042133-EE8C-48AA-ABB3-317C9B37EF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36355F28-0CAE-41C1-BD08-08D0ACE4B1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>Kode Kegiatan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Tanggal Mulai</t>
   </si>
@@ -55,9 +63,6 @@
     <t>Nomor BAST</t>
   </si>
   <si>
-    <t>1.03.08.2.01</t>
-  </si>
-  <si>
     <t>5.1.02.02.01.0030</t>
   </si>
   <si>
@@ -76,16 +81,24 @@
     <t>PAD-SP3/PT AMNT</t>
   </si>
   <si>
-    <t>Sub Rek</t>
+    <t>1 Januari 2025</t>
+  </si>
+  <si>
+    <t>Kode Sub Kegiatan</t>
+  </si>
+  <si>
+    <t>Kode Rekening</t>
+  </si>
+  <si>
+    <t>1.03.08.2.01.0018</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Rp&quot;\ #,##0;\-&quot;Rp&quot;\ #,##0;&quot;Rp&quot;\ 0"/>
-    <numFmt numFmtId="165" formatCode="[$-13809]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -121,14 +134,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,15 +447,15 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -493,76 +503,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>45688</v>
-      </c>
-      <c r="B2" s="3">
-        <v>45727</v>
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" s="2">
+        <v>2142436160</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2139720000</v>
+      </c>
+      <c r="K2" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4">
-        <v>2142436160</v>
-      </c>
-      <c r="J2" s="4">
-        <v>2139720000</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
